--- a/artfynd/A 37667-2025 artfynd.xlsx
+++ b/artfynd/A 37667-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1105,6 +1105,108 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128418269</v>
+      </c>
+      <c r="B6" t="n">
+        <v>95816</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1079</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Aspfjädermossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neckera pennata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Försjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>542707</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6390031</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Pelarne</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37667-2025 artfynd.xlsx
+++ b/artfynd/A 37667-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128305687</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128305703</v>
       </c>
       <c r="B3" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128305637</v>
       </c>
       <c r="B4" t="n">
-        <v>100652</v>
+        <v>100660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>128305672</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128418269</v>
       </c>
       <c r="B6" t="n">
-        <v>95816</v>
+        <v>95818</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37667-2025 artfynd.xlsx
+++ b/artfynd/A 37667-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128305687</v>
       </c>
       <c r="B2" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128305703</v>
       </c>
       <c r="B3" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128305637</v>
       </c>
       <c r="B4" t="n">
-        <v>100660</v>
+        <v>100753</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>128305672</v>
       </c>
       <c r="B5" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128418269</v>
       </c>
       <c r="B6" t="n">
-        <v>95818</v>
+        <v>95911</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37667-2025 artfynd.xlsx
+++ b/artfynd/A 37667-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128305687</v>
       </c>
       <c r="B2" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128305703</v>
       </c>
       <c r="B3" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128305637</v>
       </c>
       <c r="B4" t="n">
-        <v>100753</v>
+        <v>100768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>128305672</v>
       </c>
       <c r="B5" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128418269</v>
       </c>
       <c r="B6" t="n">
-        <v>95911</v>
+        <v>95923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37667-2025 artfynd.xlsx
+++ b/artfynd/A 37667-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128305687</v>
       </c>
       <c r="B2" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128305703</v>
       </c>
       <c r="B3" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128305637</v>
       </c>
       <c r="B4" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>128305672</v>
       </c>
       <c r="B5" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128418269</v>
       </c>
       <c r="B6" t="n">
-        <v>95923</v>
+        <v>95925</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37667-2025 artfynd.xlsx
+++ b/artfynd/A 37667-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128305687</v>
       </c>
       <c r="B2" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128305703</v>
       </c>
       <c r="B3" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128305637</v>
       </c>
       <c r="B4" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>128305672</v>
       </c>
       <c r="B5" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37667-2025 artfynd.xlsx
+++ b/artfynd/A 37667-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128305687</v>
       </c>
       <c r="B2" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128305703</v>
       </c>
       <c r="B3" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128305637</v>
       </c>
       <c r="B4" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>128305672</v>
       </c>
       <c r="B5" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128418269</v>
       </c>
       <c r="B6" t="n">
-        <v>95925</v>
+        <v>95926</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37667-2025 artfynd.xlsx
+++ b/artfynd/A 37667-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128305687</v>
       </c>
       <c r="B2" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128305703</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128305637</v>
       </c>
       <c r="B4" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>128305672</v>
       </c>
       <c r="B5" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128418269</v>
       </c>
       <c r="B6" t="n">
-        <v>95926</v>
+        <v>95953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37667-2025 artfynd.xlsx
+++ b/artfynd/A 37667-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128305687</v>
       </c>
       <c r="B2" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128305703</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128305637</v>
       </c>
       <c r="B4" t="n">
-        <v>100807</v>
+        <v>100820</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>128305672</v>
       </c>
       <c r="B5" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128418269</v>
       </c>
       <c r="B6" t="n">
-        <v>95953</v>
+        <v>95966</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37667-2025 artfynd.xlsx
+++ b/artfynd/A 37667-2025 artfynd.xlsx
@@ -1110,7 +1110,7 @@
         <v>128418269</v>
       </c>
       <c r="B6" t="n">
-        <v>95966</v>
+        <v>95970</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37667-2025 artfynd.xlsx
+++ b/artfynd/A 37667-2025 artfynd.xlsx
@@ -1110,7 +1110,7 @@
         <v>128418269</v>
       </c>
       <c r="B6" t="n">
-        <v>95970</v>
+        <v>95977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
